--- a/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T10:53:52+00:00</t>
+    <t>2025-11-20T14:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T14:13:30+00:00</t>
+    <t>2025-11-20T14:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T14:42:10+00:00</t>
+    <t>2025-11-20T15:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T15:10:08+00:00</t>
+    <t>2025-11-20T15:24:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T15:24:16+00:00</t>
+    <t>2025-11-20T15:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T15:44:38+00:00</t>
+    <t>2025-12-01T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-01T08:27:40+00:00</t>
+    <t>2025-12-22T09:32:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/basis/migrate-ig-to-ig-publisher-ptdata-1885/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T09:32:22+00:00</t>
+    <t>2025-12-22T10:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
